--- a/output/pdf_financials_xlsx/RSMX.xlsx
+++ b/output/pdf_financials_xlsx/RSMX.xlsx
@@ -2753,22 +2753,22 @@
         </is>
       </c>
       <c r="B92" s="3" t="n">
-        <v>0</v>
+        <v>0.007379</v>
       </c>
       <c r="C92" s="3" t="n">
-        <v>0</v>
+        <v>0.007379</v>
       </c>
       <c r="D92" s="3" t="n">
-        <v>0</v>
+        <v>1.201261</v>
       </c>
       <c r="E92" s="3" t="n">
-        <v>0</v>
+        <v>1.866976</v>
       </c>
       <c r="F92" s="3" t="n">
-        <v>0</v>
+        <v>2.470418</v>
       </c>
       <c r="G92" s="3" t="n">
-        <v>0</v>
+        <v>5.140657</v>
       </c>
     </row>
     <row r="93">
@@ -4506,7 +4506,11 @@
           <t>Reserves 6</t>
         </is>
       </c>
-      <c r="D16" t="inlineStr"/>
+      <c r="D16" t="inlineStr">
+        <is>
+          <t>AdditionalPaidInCapital</t>
+        </is>
+      </c>
       <c r="E16" t="inlineStr">
         <is>
           <t>-</t>
@@ -5126,7 +5130,11 @@
           <t>Reserves 6</t>
         </is>
       </c>
-      <c r="D30" t="inlineStr"/>
+      <c r="D30" t="inlineStr">
+        <is>
+          <t>AdditionalPaidInCapital</t>
+        </is>
+      </c>
       <c r="E30" s="5" t="n">
         <v>0.007379</v>
       </c>

--- a/output/pdf_financials_xlsx/RSMX.xlsx
+++ b/output/pdf_financials_xlsx/RSMX.xlsx
@@ -1279,22 +1279,22 @@
         </is>
       </c>
       <c r="B34" s="3" t="n">
-        <v>0</v>
+        <v>0.012798</v>
       </c>
       <c r="C34" s="3" t="n">
-        <v>0</v>
+        <v>0.001478</v>
       </c>
       <c r="D34" s="3" t="n">
-        <v>0</v>
+        <v>1.110463</v>
       </c>
       <c r="E34" s="3" t="n">
-        <v>0</v>
+        <v>0.057886</v>
       </c>
       <c r="F34" s="3" t="n">
-        <v>0</v>
+        <v>0.014973</v>
       </c>
       <c r="G34" s="3" t="n">
-        <v>0</v>
+        <v>3.517828</v>
       </c>
     </row>
     <row r="35">
@@ -1329,22 +1329,22 @@
         </is>
       </c>
       <c r="B36" s="3" t="n">
-        <v>0</v>
+        <v>0.012798</v>
       </c>
       <c r="C36" s="3" t="n">
-        <v>0</v>
+        <v>0.001478</v>
       </c>
       <c r="D36" s="3" t="n">
-        <v>0</v>
+        <v>1.110463</v>
       </c>
       <c r="E36" s="3" t="n">
-        <v>0</v>
+        <v>0.057886</v>
       </c>
       <c r="F36" s="3" t="n">
-        <v>0</v>
+        <v>0.014973</v>
       </c>
       <c r="G36" s="3" t="n">
-        <v>0</v>
+        <v>3.517828</v>
       </c>
     </row>
     <row r="37">
@@ -1629,22 +1629,22 @@
         </is>
       </c>
       <c r="B48" s="3" t="n">
-        <v>0.027182</v>
+        <v>0.014384</v>
       </c>
       <c r="C48" s="3" t="n">
-        <v>0.011478</v>
+        <v>0.01</v>
       </c>
       <c r="D48" s="3" t="n">
-        <v>1.381029</v>
+        <v>0.270566</v>
       </c>
       <c r="E48" s="3" t="n">
-        <v>0.160375</v>
+        <v>0.102489</v>
       </c>
       <c r="F48" s="3" t="n">
-        <v>0.088436</v>
+        <v>0.073463</v>
       </c>
       <c r="G48" s="3" t="n">
-        <v>3.786441</v>
+        <v>0.268613</v>
       </c>
     </row>
     <row r="49">
@@ -3970,7 +3970,7 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>Cash</t>
+          <t>CashAndCashEquivalents</t>
         </is>
       </c>
       <c r="E3" s="5" t="n">
@@ -8208,7 +8208,7 @@
       </c>
       <c r="D100" t="inlineStr">
         <is>
-          <t>InterestExpense</t>
+          <t>InterestExpenseOperating</t>
         </is>
       </c>
       <c r="E100" t="inlineStr">
@@ -8492,7 +8492,7 @@
       </c>
       <c r="D106" t="inlineStr">
         <is>
-          <t>InterestExpense</t>
+          <t>InterestExpenseOperating</t>
         </is>
       </c>
       <c r="E106" t="inlineStr">

--- a/output/pdf_financials_xlsx/RSMX.xlsx
+++ b/output/pdf_financials_xlsx/RSMX.xlsx
@@ -3435,10 +3435,10 @@
         </is>
       </c>
       <c r="B120" s="3" t="n">
-        <v>0</v>
+        <v>0.86065</v>
       </c>
       <c r="C120" s="3" t="n">
-        <v>0</v>
+        <v>0.729525</v>
       </c>
       <c r="D120" s="3" t="n">
         <v>0.035</v>
@@ -6792,7 +6792,11 @@
           <t>Proceeds from issuance of common shares, net of issuance costs</t>
         </is>
       </c>
-      <c r="D68" t="inlineStr"/>
+      <c r="D68" t="inlineStr">
+        <is>
+          <t>IssuanceOfCapitalStock</t>
+        </is>
+      </c>
       <c r="E68" s="5" t="n">
         <v>0.86065</v>
       </c>
